--- a/output/tables/df_ports_stats.xlsx
+++ b/output/tables/df_ports_stats.xlsx
@@ -597,34 +597,34 @@
         <v>0.2228320520286289</v>
       </c>
       <c r="H2" t="n">
-        <v>0.103434623457366</v>
+        <v>0.1034346234573659</v>
       </c>
       <c r="I2" t="n">
-        <v>3.630296648691393</v>
+        <v>3.630296648691391</v>
       </c>
       <c r="J2" t="n">
         <v>0.9151992294042315</v>
       </c>
       <c r="K2" t="n">
-        <v>14.65122594991079</v>
+        <v>14.65122594991078</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3706190930848885</v>
+        <v>0.3706190930848887</v>
       </c>
       <c r="M2" t="n">
-        <v>3.06209622735656</v>
+        <v>3.062096227356563</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6991472948704673</v>
+        <v>0.6991472948704683</v>
       </c>
       <c r="O2" t="n">
-        <v>7.998270429429073</v>
+        <v>7.998270429429086</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3648363821556061</v>
+        <v>-0.364836382155606</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.206305469441445</v>
+        <v>-3.206305469441443</v>
       </c>
       <c r="R2" t="n">
         <v>0.7152885280862014</v>
@@ -702,34 +702,34 @@
         <v>0.7471515310946628</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07452703821191624</v>
+        <v>0.07452703821191622</v>
       </c>
       <c r="I3" t="n">
-        <v>3.004627473591152</v>
+        <v>3.004627473591151</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7630049465440194</v>
+        <v>0.7630049465440195</v>
       </c>
       <c r="K3" t="n">
         <v>15.29057758874939</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0208418257452088</v>
+        <v>0.02084182574520912</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2613072753935349</v>
+        <v>0.2613072753935389</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1177628682114756</v>
+        <v>0.1177628682114758</v>
       </c>
       <c r="O3" t="n">
-        <v>1.515068352188926</v>
+        <v>1.515068352188928</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07632096924953821</v>
+        <v>0.07632096924953843</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.638225946142962</v>
+        <v>1.638225946142966</v>
       </c>
       <c r="R3" t="n">
         <v>0.4708399429007062</v>
@@ -810,31 +810,31 @@
         <v>0.0977824623520563</v>
       </c>
       <c r="I4" t="n">
-        <v>3.726033300500905</v>
+        <v>3.726033300500904</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7724668992362607</v>
+        <v>0.7724668992362604</v>
       </c>
       <c r="K4" t="n">
-        <v>13.96516366359608</v>
+        <v>13.96516366359607</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2052177956977403</v>
+        <v>0.2052177956977406</v>
       </c>
       <c r="M4" t="n">
-        <v>2.937308844240286</v>
+        <v>2.93730884424029</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5963706308733888</v>
+        <v>0.5963706308733894</v>
       </c>
       <c r="O4" t="n">
-        <v>7.334194901419076</v>
+        <v>7.334194901419078</v>
       </c>
       <c r="P4" t="n">
         <v>-0.1378853239804816</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4830607748189</v>
+        <v>-2.483060774818898</v>
       </c>
       <c r="R4" t="n">
         <v>0.591380641179256</v>
@@ -912,31 +912,31 @@
         <v>0.2371220816239188</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1017473927933845</v>
+        <v>0.1017473927933844</v>
       </c>
       <c r="I5" t="n">
-        <v>3.716679696514831</v>
+        <v>3.71667969651483</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6146359504548402</v>
+        <v>0.61463595045484</v>
       </c>
       <c r="K5" t="n">
-        <v>10.14095526437554</v>
+        <v>10.14095526437553</v>
       </c>
       <c r="L5" t="n">
         <v>0.2481935070551475</v>
       </c>
       <c r="M5" t="n">
-        <v>2.025069722807574</v>
+        <v>2.025069722807576</v>
       </c>
       <c r="N5" t="n">
-        <v>0.626989387755525</v>
+        <v>0.6269893877555259</v>
       </c>
       <c r="O5" t="n">
-        <v>7.269149118637875</v>
+        <v>7.269149118637886</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3311427509652338</v>
+        <v>-0.3311427509652339</v>
       </c>
       <c r="Q5" t="n">
         <v>-3.114103950879617</v>
@@ -1017,37 +1017,37 @@
         <v>0.8101334032030804</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07882605812933426</v>
+        <v>0.07882605812933424</v>
       </c>
       <c r="I6" t="n">
-        <v>3.29991292409335</v>
+        <v>3.299912924093349</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4307968715834936</v>
+        <v>0.4307968715834937</v>
       </c>
       <c r="K6" t="n">
         <v>9.044486053901261</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1060025340359008</v>
+        <v>-0.1060025340359006</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.513621886177809</v>
+        <v>-1.513621886177807</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03833813474023231</v>
+        <v>0.03833813474023236</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4911438545488206</v>
+        <v>0.491143854548821</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1015017459043074</v>
+        <v>0.1015017459043075</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.343657160662783</v>
+        <v>2.343657160662784</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2136196510592738</v>
+        <v>0.2136196510592737</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1122,28 +1122,28 @@
         <v>0.9731259710350344</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09066743475434727</v>
+        <v>0.09066743475434726</v>
       </c>
       <c r="I7" t="n">
         <v>3.551053331511762</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4352370862761953</v>
+        <v>0.4352370862761952</v>
       </c>
       <c r="K7" t="n">
-        <v>8.10428300890622</v>
+        <v>8.104283008906217</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07119450316127728</v>
+        <v>0.0711945031612775</v>
       </c>
       <c r="M7" t="n">
-        <v>1.103479612092257</v>
+        <v>1.10347961209226</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5176555714868633</v>
+        <v>0.5176555714868638</v>
       </c>
       <c r="O7" t="n">
-        <v>6.567720366630852</v>
+        <v>6.567720366630856</v>
       </c>
       <c r="P7" t="n">
         <v>-0.1162137493597864</v>
@@ -1152,7 +1152,7 @@
         <v>-2.113995257341653</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3877287493977855</v>
+        <v>0.3877287493977856</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1227,37 +1227,37 @@
         <v>0.6984782480513653</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3443747317864265</v>
+        <v>0.3443747317864266</v>
       </c>
       <c r="I8" t="n">
-        <v>3.842223150153312</v>
+        <v>3.842223150153314</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8842682499860337</v>
+        <v>0.8842682499860329</v>
       </c>
       <c r="K8" t="n">
-        <v>4.202025695092275</v>
+        <v>4.20202569509227</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1800712170599371</v>
+        <v>0.1800712170599376</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3711277035843697</v>
+        <v>0.3711277035843709</v>
       </c>
       <c r="N8" t="n">
-        <v>1.515473678168164</v>
+        <v>1.515473678168166</v>
       </c>
       <c r="O8" t="n">
-        <v>6.143993916713738</v>
+        <v>6.143993916713745</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.164562362502471</v>
+        <v>-1.164562362502472</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.680066729575569</v>
+        <v>-2.68006672957557</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4479238690819416</v>
+        <v>0.4479238690819415</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1335,34 +1335,34 @@
         <v>0.2674695438308263</v>
       </c>
       <c r="I9" t="n">
-        <v>3.986373539287718</v>
+        <v>3.98637353928772</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1585594365129357</v>
+        <v>0.1585594365129358</v>
       </c>
       <c r="K9" t="n">
-        <v>1.184898209966032</v>
+        <v>1.184898209966033</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6926814902610889</v>
+        <v>-0.6926814902610887</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.955303872919842</v>
+        <v>-3.95530387291984</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1342767002203001</v>
+        <v>-0.1342767002203006</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5939794210905804</v>
+        <v>-0.5939794210905824</v>
       </c>
       <c r="P9" t="n">
         <v>0.3656870648709281</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.039232016003322</v>
+        <v>3.03923201600332</v>
       </c>
       <c r="R9" t="n">
-        <v>0.07009388483289358</v>
+        <v>0.0700938848328938</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1440,28 +1440,28 @@
         <v>0.2599832314706374</v>
       </c>
       <c r="I10" t="n">
-        <v>4.597225654906017</v>
+        <v>4.597225654906018</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3826305032740539</v>
+        <v>0.3826305032740536</v>
       </c>
       <c r="K10" t="n">
-        <v>3.183259239684164</v>
+        <v>3.183259239684162</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03620967970936637</v>
+        <v>0.03620967970936656</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1347223468975744</v>
+        <v>0.1347223468975751</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5487142810344026</v>
+        <v>0.5487142810344033</v>
       </c>
       <c r="O10" t="n">
-        <v>3.31975420076438</v>
+        <v>3.319754200764385</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2524445386728309</v>
+        <v>-0.252444538672831</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.609962991172408</v>
@@ -1545,31 +1545,31 @@
         <v>0.0977824623520563</v>
       </c>
       <c r="I11" t="n">
-        <v>3.726033300500905</v>
+        <v>3.726033300500904</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7724668992362607</v>
+        <v>0.7724668992362604</v>
       </c>
       <c r="K11" t="n">
-        <v>13.96516366359608</v>
+        <v>13.96516366359607</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2052177956977403</v>
+        <v>0.2052177956977406</v>
       </c>
       <c r="M11" t="n">
-        <v>2.937308844240286</v>
+        <v>2.93730884424029</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5963706308733888</v>
+        <v>0.5963706308733894</v>
       </c>
       <c r="O11" t="n">
-        <v>7.334194901419076</v>
+        <v>7.334194901419078</v>
       </c>
       <c r="P11" t="n">
         <v>-0.1378853239804816</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4830607748189</v>
+        <v>-2.483060774818898</v>
       </c>
       <c r="R11" t="n">
         <v>0.591380641179256</v>
@@ -1647,34 +1647,34 @@
         <v>2.316853742945969</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06483237184068322</v>
+        <v>0.06483237184068318</v>
       </c>
       <c r="I12" t="n">
-        <v>2.648157601179731</v>
+        <v>2.648157601179728</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9707615704175897</v>
+        <v>0.9707615704175894</v>
       </c>
       <c r="K12" t="n">
-        <v>16.13427241660233</v>
+        <v>16.13427241660231</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2031881342619862</v>
+        <v>0.2031881342619866</v>
       </c>
       <c r="M12" t="n">
-        <v>1.93142838945246</v>
+        <v>1.931428389452463</v>
       </c>
       <c r="N12" t="n">
-        <v>0.419541080051806</v>
+        <v>0.4195410800518065</v>
       </c>
       <c r="O12" t="n">
         <v>5.432101010797401</v>
       </c>
       <c r="P12" t="n">
-        <v>0.04527376770269571</v>
+        <v>0.04527376770269594</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.748141873036399</v>
+        <v>0.7481418730364023</v>
       </c>
       <c r="R12" t="n">
         <v>0.6381325211448932</v>
@@ -1752,37 +1752,37 @@
         <v>0.8101334032030804</v>
       </c>
       <c r="H13" t="n">
-        <v>0.07882605812933426</v>
+        <v>0.07882605812933424</v>
       </c>
       <c r="I13" t="n">
-        <v>3.29991292409335</v>
+        <v>3.299912924093349</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4307968715834936</v>
+        <v>0.4307968715834937</v>
       </c>
       <c r="K13" t="n">
         <v>9.044486053901261</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1060025340359008</v>
+        <v>-0.1060025340359006</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.513621886177809</v>
+        <v>-1.513621886177807</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03833813474023231</v>
+        <v>0.03833813474023236</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4911438545488206</v>
+        <v>0.491143854548821</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1015017459043074</v>
+        <v>0.1015017459043075</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.343657160662783</v>
+        <v>2.343657160662784</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2136196510592738</v>
+        <v>0.2136196510592737</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1857,10 +1857,10 @@
         <v>2.412718548306209</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05639698344970885</v>
+        <v>0.05639698344970881</v>
       </c>
       <c r="I14" t="n">
-        <v>2.365989162713668</v>
+        <v>2.365989162713666</v>
       </c>
       <c r="J14" t="n">
         <v>0.6648623680493825</v>
@@ -1869,22 +1869,22 @@
         <v>11.60052164084876</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1177874448733583</v>
+        <v>0.1177874448733586</v>
       </c>
       <c r="M14" t="n">
-        <v>1.327348222436577</v>
+        <v>1.32734822243658</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3470982971272106</v>
+        <v>0.347098297127211</v>
       </c>
       <c r="O14" t="n">
-        <v>4.582375557670485</v>
+        <v>4.582375557670487</v>
       </c>
       <c r="P14" t="n">
-        <v>0.08293399441461619</v>
+        <v>0.08293399441461635</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.43433383734736</v>
+        <v>1.434333837347362</v>
       </c>
       <c r="R14" t="n">
         <v>0.4601514914854684</v>
@@ -1965,28 +1965,28 @@
         <v>0.2599832314706374</v>
       </c>
       <c r="I15" t="n">
-        <v>4.597225654906017</v>
+        <v>4.597225654906018</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3826305032740539</v>
+        <v>0.3826305032740536</v>
       </c>
       <c r="K15" t="n">
-        <v>3.183259239684164</v>
+        <v>3.183259239684162</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03620967970936637</v>
+        <v>0.03620967970936656</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1347223468975744</v>
+        <v>0.1347223468975751</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5487142810344026</v>
+        <v>0.5487142810344033</v>
       </c>
       <c r="O15" t="n">
-        <v>3.31975420076438</v>
+        <v>3.319754200764385</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2524445386728309</v>
+        <v>-0.252444538672831</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.609962991172408</v>
@@ -2067,34 +2067,34 @@
         <v>7.020975029305385</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1685586158602541</v>
+        <v>0.168558615860254</v>
       </c>
       <c r="I16" t="n">
-        <v>2.519314730496677</v>
+        <v>2.519314730496676</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8502104962281525</v>
+        <v>0.8502104962281527</v>
       </c>
       <c r="K16" t="n">
-        <v>5.449775465229427</v>
+        <v>5.449775465229429</v>
       </c>
       <c r="L16" t="n">
-        <v>0.007830305514628072</v>
+        <v>0.007830305514628488</v>
       </c>
       <c r="M16" t="n">
-        <v>0.03687169275630593</v>
+        <v>0.03687169275630788</v>
       </c>
       <c r="N16" t="n">
-        <v>0.719610158657974</v>
+        <v>0.7196101586579741</v>
       </c>
       <c r="O16" t="n">
         <v>3.428021522775981</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3493834822585233</v>
+        <v>0.3493834822585236</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.229577976569388</v>
+        <v>2.229577976569389</v>
       </c>
       <c r="R16" t="n">
         <v>0.1528159617370626</v>
@@ -2175,31 +2175,31 @@
         <v>0.0977824623520563</v>
       </c>
       <c r="I17" t="n">
-        <v>3.726033300500905</v>
+        <v>3.726033300500904</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7724668992362607</v>
+        <v>0.7724668992362604</v>
       </c>
       <c r="K17" t="n">
-        <v>13.96516366359608</v>
+        <v>13.96516366359607</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2052177956977403</v>
+        <v>0.2052177956977406</v>
       </c>
       <c r="M17" t="n">
-        <v>2.937308844240286</v>
+        <v>2.93730884424029</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5963706308733888</v>
+        <v>0.5963706308733894</v>
       </c>
       <c r="O17" t="n">
-        <v>7.334194901419076</v>
+        <v>7.334194901419078</v>
       </c>
       <c r="P17" t="n">
         <v>-0.1378853239804816</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4830607748189</v>
+        <v>-2.483060774818898</v>
       </c>
       <c r="R17" t="n">
         <v>0.591380641179256</v>
@@ -2280,34 +2280,34 @@
         <v>0.1169573586926704</v>
       </c>
       <c r="I18" t="n">
-        <v>4.746649516992666</v>
+        <v>4.746649516992664</v>
       </c>
       <c r="J18" t="n">
         <v>0.7859232309686279</v>
       </c>
       <c r="K18" t="n">
-        <v>15.29677294898078</v>
+        <v>15.29677294898077</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2091737112758189</v>
+        <v>0.2091737112758191</v>
       </c>
       <c r="M18" t="n">
-        <v>2.700514691978571</v>
+        <v>2.700514691978574</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4754339074993205</v>
+        <v>0.4754339074993211</v>
       </c>
       <c r="O18" t="n">
-        <v>5.926012549533326</v>
+        <v>5.926012549533331</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1634977148894132</v>
+        <v>-0.1634977148894131</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.689362752009022</v>
+        <v>-2.689362752009017</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6209528162453047</v>
+        <v>0.6209528162453049</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2382,37 +2382,37 @@
         <v>0.8101334032030804</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07882605812933426</v>
+        <v>0.07882605812933424</v>
       </c>
       <c r="I19" t="n">
-        <v>3.29991292409335</v>
+        <v>3.299912924093349</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4307968715834936</v>
+        <v>0.4307968715834937</v>
       </c>
       <c r="K19" t="n">
         <v>9.044486053901261</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1060025340359008</v>
+        <v>-0.1060025340359006</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.513621886177809</v>
+        <v>-1.513621886177807</v>
       </c>
       <c r="N19" t="n">
-        <v>0.03833813474023231</v>
+        <v>0.03833813474023236</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4911438545488206</v>
+        <v>0.491143854548821</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1015017459043074</v>
+        <v>0.1015017459043075</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.343657160662783</v>
+        <v>2.343657160662784</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2136196510592738</v>
+        <v>0.2136196510592737</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2490,31 +2490,31 @@
         <v>0.118026185165393</v>
       </c>
       <c r="I20" t="n">
-        <v>4.941358889152037</v>
+        <v>4.941358889152035</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4514042675795885</v>
+        <v>0.4514042675795884</v>
       </c>
       <c r="K20" t="n">
-        <v>9.41840748584775</v>
+        <v>9.418407485847748</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06846194813366152</v>
+        <v>0.06846194813366166</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9827008227095834</v>
+        <v>0.9827008227095858</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3665411162099903</v>
+        <v>0.3665411162099906</v>
       </c>
       <c r="O20" t="n">
-        <v>4.827747058998603</v>
+        <v>4.827747058998606</v>
       </c>
       <c r="P20" t="n">
         <v>-0.1189633043708004</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.057906158827559</v>
+        <v>-2.057906158827558</v>
       </c>
       <c r="R20" t="n">
         <v>0.3846644102401878</v>
@@ -2595,28 +2595,28 @@
         <v>0.2599832314706374</v>
       </c>
       <c r="I21" t="n">
-        <v>4.597225654906017</v>
+        <v>4.597225654906018</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3826305032740539</v>
+        <v>0.3826305032740536</v>
       </c>
       <c r="K21" t="n">
-        <v>3.183259239684164</v>
+        <v>3.183259239684162</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03620967970936637</v>
+        <v>0.03620967970936656</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1347223468975744</v>
+        <v>0.1347223468975751</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5487142810344026</v>
+        <v>0.5487142810344033</v>
       </c>
       <c r="O21" t="n">
-        <v>3.31975420076438</v>
+        <v>3.319754200764385</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2524445386728309</v>
+        <v>-0.252444538672831</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.609962991172408</v>
@@ -2697,31 +2697,31 @@
         <v>2.788246106422154</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3430319789277412</v>
+        <v>0.3430319789277413</v>
       </c>
       <c r="I22" t="n">
         <v>5.357176871475987</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2523820043373254</v>
+        <v>0.2523820043373252</v>
       </c>
       <c r="K22" t="n">
-        <v>2.002319985200463</v>
+        <v>2.00231998520046</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2274331188817208</v>
+        <v>-0.2274331188817206</v>
       </c>
       <c r="M22" t="n">
         <v>-1.30345049497981</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6130410031260654</v>
+        <v>0.6130410031260659</v>
       </c>
       <c r="O22" t="n">
-        <v>3.145480864401485</v>
+        <v>3.145480864401486</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2040526458643821</v>
+        <v>-0.2040526458643822</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.345371442690972</v>

--- a/output/tables/df_ports_stats.xlsx
+++ b/output/tables/df_ports_stats.xlsx
@@ -573,7 +573,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>1_VAL_25.0_EW_130.0_VAL_20.0_EW_30.0_I_Y</t>
+          <t>1_VAL_25_EW_130_VAL_20_EW_30_I_Y</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -597,34 +597,34 @@
         <v>0.2228320520286289</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1034346234573659</v>
+        <v>0.103434623457366</v>
       </c>
       <c r="I2" t="n">
-        <v>3.630296648691391</v>
+        <v>3.630296648691393</v>
       </c>
       <c r="J2" t="n">
         <v>0.9151992294042315</v>
       </c>
       <c r="K2" t="n">
-        <v>14.65122594991078</v>
+        <v>14.65122594991079</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3706190930848887</v>
+        <v>0.3706190930848885</v>
       </c>
       <c r="M2" t="n">
-        <v>3.062096227356563</v>
+        <v>3.06209622735656</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6991472948704683</v>
+        <v>0.6991472948704673</v>
       </c>
       <c r="O2" t="n">
-        <v>7.998270429429086</v>
+        <v>7.998270429429073</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.364836382155606</v>
+        <v>-0.3648363821556061</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.206305469441443</v>
+        <v>-3.206305469441445</v>
       </c>
       <c r="R2" t="n">
         <v>0.7152885280862014</v>
@@ -678,7 +678,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2_QLT_20.0_EW_130.0_QLT_15.0_EW_30.0_I_M</t>
+          <t>2_QLT_20_EW_130_QLT_15_EW_30_I_M</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -702,34 +702,34 @@
         <v>0.7471515310946628</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07452703821191622</v>
+        <v>0.07452703821191624</v>
       </c>
       <c r="I3" t="n">
-        <v>3.004627473591151</v>
+        <v>3.004627473591152</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7630049465440195</v>
+        <v>0.7630049465440194</v>
       </c>
       <c r="K3" t="n">
         <v>15.29057758874939</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02084182574520912</v>
+        <v>0.0208418257452088</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2613072753935389</v>
+        <v>0.2613072753935349</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1177628682114758</v>
+        <v>0.1177628682114756</v>
       </c>
       <c r="O3" t="n">
-        <v>1.515068352188928</v>
+        <v>1.515068352188926</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07632096924953843</v>
+        <v>0.07632096924953821</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.638225946142966</v>
+        <v>1.638225946142962</v>
       </c>
       <c r="R3" t="n">
         <v>0.4708399429007062</v>
@@ -783,61 +783,61 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>3_VQ_20.0_EW_130.0_VQ_15.0_EW_30.0_I_M</t>
+          <t>3_VQ_25_EW_130_VQ_20_EW_30_I_M</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.193181733636707</v>
+        <v>0.1974987468703351</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1953709190157635</v>
+        <v>0.1952805544592127</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7861033484943343</v>
+        <v>0.8085738352576965</v>
       </c>
       <c r="E4" t="n">
-        <v>0.496034456554492</v>
+        <v>0.4089312897944148</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2017-12_2020-03</t>
+          <t>2007-05_2009-02</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.9257323450450525</v>
+        <v>0.90916746224333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0977824623520563</v>
+        <v>0.1032515517448015</v>
       </c>
       <c r="I4" t="n">
-        <v>3.726033300500904</v>
+        <v>4.169549904783453</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7724668992362604</v>
+        <v>0.8003599385743806</v>
       </c>
       <c r="K4" t="n">
-        <v>13.96516366359607</v>
+        <v>15.02761421798034</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2052177956977406</v>
+        <v>0.2384651847936584</v>
       </c>
       <c r="M4" t="n">
-        <v>2.93730884424029</v>
+        <v>3.06245216811059</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5963706308733894</v>
+        <v>0.5274877701549222</v>
       </c>
       <c r="O4" t="n">
-        <v>7.334194901419078</v>
+        <v>6.412758050078818</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1378853239804816</v>
+        <v>-0.1882134918440016</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.483060774818898</v>
+        <v>-2.985580478048793</v>
       </c>
       <c r="R4" t="n">
-        <v>0.591380641179256</v>
+        <v>0.6430352687834047</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -882,13 +882,13 @@
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>12546.4304305179</v>
+        <v>14227.97770470703</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4_VAL_25.0_EW_120.0_VAL_20.0_EW_50.0_I_Y</t>
+          <t>4_VAL_25_EW_120_VAL_20_EW_50_I_Y</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -912,31 +912,31 @@
         <v>0.2371220816239188</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1017473927933844</v>
+        <v>0.1017473927933845</v>
       </c>
       <c r="I5" t="n">
-        <v>3.71667969651483</v>
+        <v>3.716679696514831</v>
       </c>
       <c r="J5" t="n">
-        <v>0.61463595045484</v>
+        <v>0.6146359504548402</v>
       </c>
       <c r="K5" t="n">
-        <v>10.14095526437553</v>
+        <v>10.14095526437554</v>
       </c>
       <c r="L5" t="n">
         <v>0.2481935070551475</v>
       </c>
       <c r="M5" t="n">
-        <v>2.025069722807576</v>
+        <v>2.025069722807574</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6269893877555259</v>
+        <v>0.626989387755525</v>
       </c>
       <c r="O5" t="n">
-        <v>7.269149118637886</v>
+        <v>7.269149118637875</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3311427509652339</v>
+        <v>-0.3311427509652338</v>
       </c>
       <c r="Q5" t="n">
         <v>-3.114103950879617</v>
@@ -993,7 +993,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>5_QLT_20.0_EW_120.0_QLT_15.0_EW_50.0_I_M</t>
+          <t>5_QLT_20_EW_120_QLT_15_EW_50_I_M</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1017,37 +1017,37 @@
         <v>0.8101334032030804</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07882605812933424</v>
+        <v>0.07882605812933426</v>
       </c>
       <c r="I6" t="n">
-        <v>3.299912924093349</v>
+        <v>3.29991292409335</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4307968715834937</v>
+        <v>0.4307968715834936</v>
       </c>
       <c r="K6" t="n">
         <v>9.044486053901261</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1060025340359006</v>
+        <v>-0.1060025340359008</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.513621886177807</v>
+        <v>-1.513621886177809</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03833813474023236</v>
+        <v>0.03833813474023231</v>
       </c>
       <c r="O6" t="n">
-        <v>0.491143854548821</v>
+        <v>0.4911438545488206</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1015017459043075</v>
+        <v>0.1015017459043074</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.343657160662784</v>
+        <v>2.343657160662783</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2136196510592737</v>
+        <v>0.2136196510592738</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1098,61 +1098,61 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6_VQ_20.0_EW_120.0_VQ_15.0_EW_50.0_I_M</t>
+          <t>6_VQ_25_EW_120_VQ_15_EW_50_I_Y</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.155007377708289</v>
+        <v>0.1538677607058452</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1572949135900514</v>
+        <v>0.1412576844428378</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7337006332516798</v>
+        <v>0.8089312886343218</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2273480989264647</v>
+        <v>0.3121166842072419</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2007-05_2009-01</t>
+          <t>2007-05_2009-02</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.9731259710350344</v>
+        <v>0.2408731844284395</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09066743475434726</v>
+        <v>0.09210094311620436</v>
       </c>
       <c r="I7" t="n">
-        <v>3.551053331511762</v>
+        <v>4.15072355108735</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4352370862761952</v>
+        <v>0.4567344818767068</v>
       </c>
       <c r="K7" t="n">
-        <v>8.104283008906217</v>
+        <v>9.982338415574048</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0711945031612775</v>
+        <v>0.1613306757696474</v>
       </c>
       <c r="M7" t="n">
-        <v>1.10347961209226</v>
+        <v>1.706362123277361</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5176555714868638</v>
+        <v>0.2735681298058212</v>
       </c>
       <c r="O7" t="n">
-        <v>6.567720366630856</v>
+        <v>4.152643564880442</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1162137493597864</v>
+        <v>-0.1234984588076339</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.113995257341653</v>
+        <v>-2.004781037397805</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3877287493977856</v>
+        <v>0.4147422741011032</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>5295.92808904543</v>
+        <v>5509.14021936117</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>7_VAL_25.0_EW_300.0_VAL_20.0_EW_200.0_I_Y</t>
+          <t>7_VAL_25_EW_300_VAL_20_EW_200_I_Y</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1227,37 +1227,37 @@
         <v>0.6984782480513653</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3443747317864266</v>
+        <v>0.3443747317864265</v>
       </c>
       <c r="I8" t="n">
-        <v>3.842223150153314</v>
+        <v>3.842223150153312</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8842682499860329</v>
+        <v>0.8842682499860337</v>
       </c>
       <c r="K8" t="n">
-        <v>4.20202569509227</v>
+        <v>4.202025695092275</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1800712170599376</v>
+        <v>0.1800712170599371</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3711277035843709</v>
+        <v>0.3711277035843697</v>
       </c>
       <c r="N8" t="n">
-        <v>1.515473678168166</v>
+        <v>1.515473678168164</v>
       </c>
       <c r="O8" t="n">
-        <v>6.143993916713745</v>
+        <v>6.143993916713738</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.164562362502472</v>
+        <v>-1.164562362502471</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.68006672957557</v>
+        <v>-2.680066729575569</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4479238690819415</v>
+        <v>0.4479238690819416</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8_QLT_20.0_EW_300.0_QLT_15.0_EW_200.0_I_M</t>
+          <t>8_QLT_20_EW_300_QLT_15_EW_200_I_M</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1335,34 +1335,34 @@
         <v>0.2674695438308263</v>
       </c>
       <c r="I9" t="n">
-        <v>3.98637353928772</v>
+        <v>3.986373539287718</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1585594365129358</v>
+        <v>0.1585594365129357</v>
       </c>
       <c r="K9" t="n">
-        <v>1.184898209966033</v>
+        <v>1.184898209966032</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6926814902610887</v>
+        <v>-0.6926814902610889</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.95530387291984</v>
+        <v>-3.955303872919842</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1342767002203006</v>
+        <v>-0.1342767002203001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5939794210905824</v>
+        <v>-0.5939794210905804</v>
       </c>
       <c r="P9" t="n">
         <v>0.3656870648709281</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.03923201600332</v>
+        <v>3.039232016003322</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0700938848328938</v>
+        <v>0.07009388483289358</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>9_VQ_25.0_EW_300.0_VQ_20.0_EW_200.0_I_Y</t>
+          <t>9_VQ_25_EW_300_VQ_20_EW_200_I_Y</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1440,28 +1440,28 @@
         <v>0.2599832314706374</v>
       </c>
       <c r="I10" t="n">
-        <v>4.597225654906018</v>
+        <v>4.597225654906017</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3826305032740536</v>
+        <v>0.3826305032740539</v>
       </c>
       <c r="K10" t="n">
-        <v>3.183259239684162</v>
+        <v>3.183259239684164</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03620967970936656</v>
+        <v>0.03620967970936637</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1347223468975751</v>
+        <v>0.1347223468975744</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5487142810344033</v>
+        <v>0.5487142810344026</v>
       </c>
       <c r="O10" t="n">
-        <v>3.319754200764385</v>
+        <v>3.31975420076438</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.252444538672831</v>
+        <v>-0.2524445386728309</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.609962991172408</v>
@@ -1518,61 +1518,61 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>10_VQ_20.0_EW_130.0_VQ_15.0_EW_30.0_I_M</t>
+          <t>10_VQ_25_EW_130_VQ_20_EW_30_I_M</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.193181733636707</v>
+        <v>0.1974987468703351</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1953709190157635</v>
+        <v>0.1952805544592127</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7861033484943343</v>
+        <v>0.8085738352576965</v>
       </c>
       <c r="E11" t="n">
-        <v>0.496034456554492</v>
+        <v>0.4089312897944148</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2017-12_2020-03</t>
+          <t>2007-05_2009-02</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.9257323450450525</v>
+        <v>0.90916746224333</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0977824623520563</v>
+        <v>0.1032515517448015</v>
       </c>
       <c r="I11" t="n">
-        <v>3.726033300500904</v>
+        <v>4.169549904783453</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7724668992362604</v>
+        <v>0.8003599385743806</v>
       </c>
       <c r="K11" t="n">
-        <v>13.96516366359607</v>
+        <v>15.02761421798034</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2052177956977406</v>
+        <v>0.2384651847936584</v>
       </c>
       <c r="M11" t="n">
-        <v>2.93730884424029</v>
+        <v>3.06245216811059</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5963706308733894</v>
+        <v>0.5274877701549222</v>
       </c>
       <c r="O11" t="n">
-        <v>7.334194901419078</v>
+        <v>6.412758050078818</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1378853239804816</v>
+        <v>-0.1882134918440016</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.483060774818898</v>
+        <v>-2.985580478048793</v>
       </c>
       <c r="R11" t="n">
-        <v>0.591380641179256</v>
+        <v>0.6430352687834047</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1617,13 +1617,13 @@
         </is>
       </c>
       <c r="AC11" t="n">
-        <v>12546.4304305179</v>
+        <v>14227.97770470703</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>11_VQAM_25.0_EW_130.0_VQAM_15.0_EW_30.0_I_M</t>
+          <t>11_VQAM_25_EW_130_VQAM_15_EW_30_I_M</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1647,34 +1647,34 @@
         <v>2.316853742945969</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06483237184068318</v>
+        <v>0.06483237184068322</v>
       </c>
       <c r="I12" t="n">
-        <v>2.648157601179728</v>
+        <v>2.648157601179731</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9707615704175894</v>
+        <v>0.9707615704175897</v>
       </c>
       <c r="K12" t="n">
-        <v>16.13427241660231</v>
+        <v>16.13427241660233</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2031881342619866</v>
+        <v>0.2031881342619862</v>
       </c>
       <c r="M12" t="n">
-        <v>1.931428389452463</v>
+        <v>1.93142838945246</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4195410800518065</v>
+        <v>0.419541080051806</v>
       </c>
       <c r="O12" t="n">
         <v>5.432101010797401</v>
       </c>
       <c r="P12" t="n">
-        <v>0.04527376770269594</v>
+        <v>0.04527376770269571</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7481418730364023</v>
+        <v>0.748141873036399</v>
       </c>
       <c r="R12" t="n">
         <v>0.6381325211448932</v>
@@ -1728,7 +1728,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>12_QLT_20.0_EW_120.0_QLT_15.0_EW_50.0_I_M</t>
+          <t>12_QLT_20_EW_120_QLT_15_EW_50_I_M</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1752,37 +1752,37 @@
         <v>0.8101334032030804</v>
       </c>
       <c r="H13" t="n">
-        <v>0.07882605812933424</v>
+        <v>0.07882605812933426</v>
       </c>
       <c r="I13" t="n">
-        <v>3.299912924093349</v>
+        <v>3.29991292409335</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4307968715834937</v>
+        <v>0.4307968715834936</v>
       </c>
       <c r="K13" t="n">
         <v>9.044486053901261</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1060025340359006</v>
+        <v>-0.1060025340359008</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.513621886177807</v>
+        <v>-1.513621886177809</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03833813474023236</v>
+        <v>0.03833813474023231</v>
       </c>
       <c r="O13" t="n">
-        <v>0.491143854548821</v>
+        <v>0.4911438545488206</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1015017459043075</v>
+        <v>0.1015017459043074</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.343657160662784</v>
+        <v>2.343657160662783</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2136196510592737</v>
+        <v>0.2136196510592738</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>13_VQAM_25.0_EW_120.0_VQAM_20.0_EW_50.0_I_M</t>
+          <t>13_VQAM_25_EW_120_VQAM_20_EW_50_I_M</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1857,10 +1857,10 @@
         <v>2.412718548306209</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05639698344970881</v>
+        <v>0.05639698344970885</v>
       </c>
       <c r="I14" t="n">
-        <v>2.365989162713666</v>
+        <v>2.365989162713668</v>
       </c>
       <c r="J14" t="n">
         <v>0.6648623680493825</v>
@@ -1869,22 +1869,22 @@
         <v>11.60052164084876</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1177874448733586</v>
+        <v>0.1177874448733583</v>
       </c>
       <c r="M14" t="n">
-        <v>1.32734822243658</v>
+        <v>1.327348222436577</v>
       </c>
       <c r="N14" t="n">
-        <v>0.347098297127211</v>
+        <v>0.3470982971272106</v>
       </c>
       <c r="O14" t="n">
-        <v>4.582375557670487</v>
+        <v>4.582375557670485</v>
       </c>
       <c r="P14" t="n">
-        <v>0.08293399441461635</v>
+        <v>0.08293399441461619</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.434333837347362</v>
+        <v>1.43433383734736</v>
       </c>
       <c r="R14" t="n">
         <v>0.4601514914854684</v>
@@ -1938,7 +1938,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>14_VQ_25.0_EW_300.0_VQ_20.0_EW_200.0_I_Y</t>
+          <t>14_VQ_25_EW_300_VQ_20_EW_200_I_Y</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1965,28 +1965,28 @@
         <v>0.2599832314706374</v>
       </c>
       <c r="I15" t="n">
-        <v>4.597225654906018</v>
+        <v>4.597225654906017</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3826305032740536</v>
+        <v>0.3826305032740539</v>
       </c>
       <c r="K15" t="n">
-        <v>3.183259239684162</v>
+        <v>3.183259239684164</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03620967970936656</v>
+        <v>0.03620967970936637</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1347223468975751</v>
+        <v>0.1347223468975744</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5487142810344033</v>
+        <v>0.5487142810344026</v>
       </c>
       <c r="O15" t="n">
-        <v>3.319754200764385</v>
+        <v>3.31975420076438</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.252444538672831</v>
+        <v>-0.2524445386728309</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.609962991172408</v>
@@ -2043,7 +2043,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>15_VQAM_25.0_EW_300.0_VQAM_20.0_EW_200.0_I_M</t>
+          <t>15_VQAM_25_EW_300_VQAM_20_EW_200_I_M</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2067,34 +2067,34 @@
         <v>7.020975029305385</v>
       </c>
       <c r="H16" t="n">
-        <v>0.168558615860254</v>
+        <v>0.1685586158602541</v>
       </c>
       <c r="I16" t="n">
-        <v>2.519314730496676</v>
+        <v>2.519314730496677</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8502104962281527</v>
+        <v>0.8502104962281525</v>
       </c>
       <c r="K16" t="n">
-        <v>5.449775465229429</v>
+        <v>5.449775465229427</v>
       </c>
       <c r="L16" t="n">
-        <v>0.007830305514628488</v>
+        <v>0.007830305514628072</v>
       </c>
       <c r="M16" t="n">
-        <v>0.03687169275630788</v>
+        <v>0.03687169275630593</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7196101586579741</v>
+        <v>0.719610158657974</v>
       </c>
       <c r="O16" t="n">
         <v>3.428021522775981</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3493834822585236</v>
+        <v>0.3493834822585233</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.229577976569389</v>
+        <v>2.229577976569388</v>
       </c>
       <c r="R16" t="n">
         <v>0.1528159617370626</v>
@@ -2148,61 +2148,61 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>16_VQ_20.0_EW_130.0_VQ_15.0_EW_30.0_I_M</t>
+          <t>16_VQ_25_EW_130_VQ_20_EW_30_I_M</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.193181733636707</v>
+        <v>0.1974987468703351</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1953709190157635</v>
+        <v>0.1952805544592127</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7861033484943343</v>
+        <v>0.8085738352576965</v>
       </c>
       <c r="E17" t="n">
-        <v>0.496034456554492</v>
+        <v>0.4089312897944148</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2017-12_2020-03</t>
+          <t>2007-05_2009-02</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.9257323450450525</v>
+        <v>0.90916746224333</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0977824623520563</v>
+        <v>0.1032515517448015</v>
       </c>
       <c r="I17" t="n">
-        <v>3.726033300500904</v>
+        <v>4.169549904783453</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7724668992362604</v>
+        <v>0.8003599385743806</v>
       </c>
       <c r="K17" t="n">
-        <v>13.96516366359607</v>
+        <v>15.02761421798034</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2052177956977406</v>
+        <v>0.2384651847936584</v>
       </c>
       <c r="M17" t="n">
-        <v>2.93730884424029</v>
+        <v>3.06245216811059</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5963706308733894</v>
+        <v>0.5274877701549222</v>
       </c>
       <c r="O17" t="n">
-        <v>7.334194901419078</v>
+        <v>6.412758050078818</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1378853239804816</v>
+        <v>-0.1882134918440016</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.483060774818898</v>
+        <v>-2.985580478048793</v>
       </c>
       <c r="R17" t="n">
-        <v>0.591380641179256</v>
+        <v>0.6430352687834047</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2247,13 +2247,13 @@
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>12546.4304305179</v>
+        <v>14227.97770470703</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>17_VQ_25.0_EW_130.0_QLT_15.0_EW_30.0_I_M</t>
+          <t>17_VQ_25_EW_130_QLT_15_EW_30_I_M</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2280,34 +2280,34 @@
         <v>0.1169573586926704</v>
       </c>
       <c r="I18" t="n">
-        <v>4.746649516992664</v>
+        <v>4.746649516992666</v>
       </c>
       <c r="J18" t="n">
         <v>0.7859232309686279</v>
       </c>
       <c r="K18" t="n">
-        <v>15.29677294898077</v>
+        <v>15.29677294898078</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2091737112758191</v>
+        <v>0.2091737112758189</v>
       </c>
       <c r="M18" t="n">
-        <v>2.700514691978574</v>
+        <v>2.700514691978571</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4754339074993211</v>
+        <v>0.4754339074993205</v>
       </c>
       <c r="O18" t="n">
-        <v>5.926012549533331</v>
+        <v>5.926012549533326</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1634977148894131</v>
+        <v>-0.1634977148894132</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.689362752009017</v>
+        <v>-2.689362752009022</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6209528162453049</v>
+        <v>0.6209528162453047</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>18_QLT_20.0_EW_120.0_QLT_15.0_EW_50.0_I_M</t>
+          <t>18_QLT_20_EW_120_QLT_15_EW_50_I_M</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2382,37 +2382,37 @@
         <v>0.8101334032030804</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07882605812933424</v>
+        <v>0.07882605812933426</v>
       </c>
       <c r="I19" t="n">
-        <v>3.299912924093349</v>
+        <v>3.29991292409335</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4307968715834937</v>
+        <v>0.4307968715834936</v>
       </c>
       <c r="K19" t="n">
         <v>9.044486053901261</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1060025340359006</v>
+        <v>-0.1060025340359008</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.513621886177807</v>
+        <v>-1.513621886177809</v>
       </c>
       <c r="N19" t="n">
-        <v>0.03833813474023236</v>
+        <v>0.03833813474023231</v>
       </c>
       <c r="O19" t="n">
-        <v>0.491143854548821</v>
+        <v>0.4911438545488206</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1015017459043075</v>
+        <v>0.1015017459043074</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.343657160662784</v>
+        <v>2.343657160662783</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2136196510592737</v>
+        <v>0.2136196510592738</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>19_VQ_25.0_EW_120.0_QLT_15.0_EW_50.0_I_M</t>
+          <t>19_VQ_25_EW_120_QLT_15_EW_50_I_M</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2490,31 +2490,31 @@
         <v>0.118026185165393</v>
       </c>
       <c r="I20" t="n">
-        <v>4.941358889152035</v>
+        <v>4.941358889152037</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4514042675795884</v>
+        <v>0.4514042675795885</v>
       </c>
       <c r="K20" t="n">
-        <v>9.418407485847748</v>
+        <v>9.41840748584775</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06846194813366166</v>
+        <v>0.06846194813366152</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9827008227095858</v>
+        <v>0.9827008227095834</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3665411162099906</v>
+        <v>0.3665411162099903</v>
       </c>
       <c r="O20" t="n">
-        <v>4.827747058998606</v>
+        <v>4.827747058998603</v>
       </c>
       <c r="P20" t="n">
         <v>-0.1189633043708004</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.057906158827558</v>
+        <v>-2.057906158827559</v>
       </c>
       <c r="R20" t="n">
         <v>0.3846644102401878</v>
@@ -2568,7 +2568,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>20_VQ_25.0_EW_300.0_VQ_20.0_EW_200.0_I_Y</t>
+          <t>20_VQ_25_EW_300_VQ_20_EW_200_I_Y</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2595,28 +2595,28 @@
         <v>0.2599832314706374</v>
       </c>
       <c r="I21" t="n">
-        <v>4.597225654906018</v>
+        <v>4.597225654906017</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3826305032740536</v>
+        <v>0.3826305032740539</v>
       </c>
       <c r="K21" t="n">
-        <v>3.183259239684162</v>
+        <v>3.183259239684164</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03620967970936656</v>
+        <v>0.03620967970936637</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1347223468975751</v>
+        <v>0.1347223468975744</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5487142810344033</v>
+        <v>0.5487142810344026</v>
       </c>
       <c r="O21" t="n">
-        <v>3.319754200764385</v>
+        <v>3.31975420076438</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.252444538672831</v>
+        <v>-0.2524445386728309</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.609962991172408</v>
@@ -2673,7 +2673,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>21_VQ_25.0_EW_300.0_QLT_20.0_EW_200.0_I_M</t>
+          <t>21_VQ_25_EW_300_QLT_20_EW_200_I_M</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2697,31 +2697,31 @@
         <v>2.788246106422154</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3430319789277413</v>
+        <v>0.3430319789277412</v>
       </c>
       <c r="I22" t="n">
         <v>5.357176871475987</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2523820043373252</v>
+        <v>0.2523820043373254</v>
       </c>
       <c r="K22" t="n">
-        <v>2.00231998520046</v>
+        <v>2.002319985200463</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2274331188817206</v>
+        <v>-0.2274331188817208</v>
       </c>
       <c r="M22" t="n">
         <v>-1.30345049497981</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6130410031260659</v>
+        <v>0.6130410031260654</v>
       </c>
       <c r="O22" t="n">
-        <v>3.145480864401486</v>
+        <v>3.145480864401485</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2040526458643822</v>
+        <v>-0.2040526458643821</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.345371442690972</v>

--- a/output/tables/df_ports_stats.xlsx
+++ b/output/tables/df_ports_stats.xlsx
@@ -597,34 +597,34 @@
         <v>0.2228320520286289</v>
       </c>
       <c r="H2" t="n">
-        <v>0.103434623457366</v>
+        <v>0.1034346234573659</v>
       </c>
       <c r="I2" t="n">
-        <v>3.630296648691393</v>
+        <v>3.630296648691391</v>
       </c>
       <c r="J2" t="n">
         <v>0.9151992294042315</v>
       </c>
       <c r="K2" t="n">
-        <v>14.65122594991079</v>
+        <v>14.65122594991078</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3706190930848885</v>
+        <v>0.3706190930848887</v>
       </c>
       <c r="M2" t="n">
-        <v>3.06209622735656</v>
+        <v>3.062096227356563</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6991472948704673</v>
+        <v>0.6991472948704683</v>
       </c>
       <c r="O2" t="n">
-        <v>7.998270429429073</v>
+        <v>7.998270429429086</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3648363821556061</v>
+        <v>-0.364836382155606</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.206305469441445</v>
+        <v>-3.206305469441443</v>
       </c>
       <c r="R2" t="n">
         <v>0.7152885280862014</v>
@@ -702,34 +702,34 @@
         <v>0.7471515310946628</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07452703821191624</v>
+        <v>0.07452703821191622</v>
       </c>
       <c r="I3" t="n">
-        <v>3.004627473591152</v>
+        <v>3.004627473591151</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7630049465440194</v>
+        <v>0.7630049465440195</v>
       </c>
       <c r="K3" t="n">
         <v>15.29057758874939</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0208418257452088</v>
+        <v>0.02084182574520912</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2613072753935349</v>
+        <v>0.2613072753935389</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1177628682114756</v>
+        <v>0.1177628682114758</v>
       </c>
       <c r="O3" t="n">
-        <v>1.515068352188926</v>
+        <v>1.515068352188928</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07632096924953821</v>
+        <v>0.07632096924953843</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.638225946142962</v>
+        <v>1.638225946142966</v>
       </c>
       <c r="R3" t="n">
         <v>0.4708399429007062</v>
@@ -807,34 +807,34 @@
         <v>0.90916746224333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1032515517448015</v>
+        <v>0.1032515517448014</v>
       </c>
       <c r="I4" t="n">
         <v>4.169549904783453</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8003599385743806</v>
+        <v>0.8003599385743805</v>
       </c>
       <c r="K4" t="n">
         <v>15.02761421798034</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2384651847936584</v>
+        <v>0.2384651847936587</v>
       </c>
       <c r="M4" t="n">
-        <v>3.06245216811059</v>
+        <v>3.062452168110595</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5274877701549222</v>
+        <v>0.527487770154923</v>
       </c>
       <c r="O4" t="n">
-        <v>6.412758050078818</v>
+        <v>6.412758050078825</v>
       </c>
       <c r="P4" t="n">
         <v>-0.1882134918440016</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.985580478048793</v>
+        <v>-2.985580478048792</v>
       </c>
       <c r="R4" t="n">
         <v>0.6430352687834047</v>
@@ -912,31 +912,31 @@
         <v>0.2371220816239188</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1017473927933845</v>
+        <v>0.1017473927933844</v>
       </c>
       <c r="I5" t="n">
-        <v>3.716679696514831</v>
+        <v>3.71667969651483</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6146359504548402</v>
+        <v>0.61463595045484</v>
       </c>
       <c r="K5" t="n">
-        <v>10.14095526437554</v>
+        <v>10.14095526437553</v>
       </c>
       <c r="L5" t="n">
         <v>0.2481935070551475</v>
       </c>
       <c r="M5" t="n">
-        <v>2.025069722807574</v>
+        <v>2.025069722807576</v>
       </c>
       <c r="N5" t="n">
-        <v>0.626989387755525</v>
+        <v>0.6269893877555259</v>
       </c>
       <c r="O5" t="n">
-        <v>7.269149118637875</v>
+        <v>7.269149118637886</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3311427509652338</v>
+        <v>-0.3311427509652339</v>
       </c>
       <c r="Q5" t="n">
         <v>-3.114103950879617</v>
@@ -1017,37 +1017,37 @@
         <v>0.8101334032030804</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07882605812933426</v>
+        <v>0.07882605812933424</v>
       </c>
       <c r="I6" t="n">
-        <v>3.29991292409335</v>
+        <v>3.299912924093349</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4307968715834936</v>
+        <v>0.4307968715834937</v>
       </c>
       <c r="K6" t="n">
         <v>9.044486053901261</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1060025340359008</v>
+        <v>-0.1060025340359006</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.513621886177809</v>
+        <v>-1.513621886177807</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03833813474023231</v>
+        <v>0.03833813474023236</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4911438545488206</v>
+        <v>0.491143854548821</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1015017459043074</v>
+        <v>0.1015017459043075</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.343657160662783</v>
+        <v>2.343657160662784</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2136196510592738</v>
+        <v>0.2136196510592737</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1122,34 +1122,34 @@
         <v>0.2408731844284395</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09210094311620436</v>
+        <v>0.09210094311620434</v>
       </c>
       <c r="I7" t="n">
-        <v>4.15072355108735</v>
+        <v>4.150723551087348</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4567344818767068</v>
+        <v>0.4567344818767067</v>
       </c>
       <c r="K7" t="n">
-        <v>9.982338415574048</v>
+        <v>9.982338415574043</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1613306757696474</v>
+        <v>0.1613306757696475</v>
       </c>
       <c r="M7" t="n">
-        <v>1.706362123277361</v>
+        <v>1.706362123277362</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2735681298058212</v>
+        <v>0.2735681298058217</v>
       </c>
       <c r="O7" t="n">
-        <v>4.152643564880442</v>
+        <v>4.152643564880447</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1234984588076339</v>
+        <v>-0.1234984588076338</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.004781037397805</v>
+        <v>-2.004781037397802</v>
       </c>
       <c r="R7" t="n">
         <v>0.4147422741011032</v>
@@ -1227,37 +1227,37 @@
         <v>0.6984782480513653</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3443747317864265</v>
+        <v>0.3443747317864266</v>
       </c>
       <c r="I8" t="n">
-        <v>3.842223150153312</v>
+        <v>3.842223150153314</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8842682499860337</v>
+        <v>0.8842682499860329</v>
       </c>
       <c r="K8" t="n">
-        <v>4.202025695092275</v>
+        <v>4.20202569509227</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1800712170599371</v>
+        <v>0.1800712170599376</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3711277035843697</v>
+        <v>0.3711277035843709</v>
       </c>
       <c r="N8" t="n">
-        <v>1.515473678168164</v>
+        <v>1.515473678168166</v>
       </c>
       <c r="O8" t="n">
-        <v>6.143993916713738</v>
+        <v>6.143993916713745</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.164562362502471</v>
+        <v>-1.164562362502472</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.680066729575569</v>
+        <v>-2.68006672957557</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4479238690819416</v>
+        <v>0.4479238690819415</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1335,34 +1335,34 @@
         <v>0.2674695438308263</v>
       </c>
       <c r="I9" t="n">
-        <v>3.986373539287718</v>
+        <v>3.98637353928772</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1585594365129357</v>
+        <v>0.1585594365129358</v>
       </c>
       <c r="K9" t="n">
-        <v>1.184898209966032</v>
+        <v>1.184898209966033</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6926814902610889</v>
+        <v>-0.6926814902610887</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.955303872919842</v>
+        <v>-3.95530387291984</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1342767002203001</v>
+        <v>-0.1342767002203006</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5939794210905804</v>
+        <v>-0.5939794210905824</v>
       </c>
       <c r="P9" t="n">
         <v>0.3656870648709281</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.039232016003322</v>
+        <v>3.03923201600332</v>
       </c>
       <c r="R9" t="n">
-        <v>0.07009388483289358</v>
+        <v>0.0700938848328938</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1440,28 +1440,28 @@
         <v>0.2599832314706374</v>
       </c>
       <c r="I10" t="n">
-        <v>4.597225654906017</v>
+        <v>4.597225654906018</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3826305032740539</v>
+        <v>0.3826305032740536</v>
       </c>
       <c r="K10" t="n">
-        <v>3.183259239684164</v>
+        <v>3.183259239684162</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03620967970936637</v>
+        <v>0.03620967970936656</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1347223468975744</v>
+        <v>0.1347223468975751</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5487142810344026</v>
+        <v>0.5487142810344033</v>
       </c>
       <c r="O10" t="n">
-        <v>3.31975420076438</v>
+        <v>3.319754200764385</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2524445386728309</v>
+        <v>-0.252444538672831</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.609962991172408</v>
@@ -1542,34 +1542,34 @@
         <v>0.90916746224333</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1032515517448015</v>
+        <v>0.1032515517448014</v>
       </c>
       <c r="I11" t="n">
         <v>4.169549904783453</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8003599385743806</v>
+        <v>0.8003599385743805</v>
       </c>
       <c r="K11" t="n">
         <v>15.02761421798034</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2384651847936584</v>
+        <v>0.2384651847936587</v>
       </c>
       <c r="M11" t="n">
-        <v>3.06245216811059</v>
+        <v>3.062452168110595</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5274877701549222</v>
+        <v>0.527487770154923</v>
       </c>
       <c r="O11" t="n">
-        <v>6.412758050078818</v>
+        <v>6.412758050078825</v>
       </c>
       <c r="P11" t="n">
         <v>-0.1882134918440016</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.985580478048793</v>
+        <v>-2.985580478048792</v>
       </c>
       <c r="R11" t="n">
         <v>0.6430352687834047</v>
@@ -1647,34 +1647,34 @@
         <v>2.316853742945969</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06483237184068322</v>
+        <v>0.06483237184068318</v>
       </c>
       <c r="I12" t="n">
-        <v>2.648157601179731</v>
+        <v>2.648157601179728</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9707615704175897</v>
+        <v>0.9707615704175894</v>
       </c>
       <c r="K12" t="n">
-        <v>16.13427241660233</v>
+        <v>16.13427241660231</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2031881342619862</v>
+        <v>0.2031881342619866</v>
       </c>
       <c r="M12" t="n">
-        <v>1.93142838945246</v>
+        <v>1.931428389452463</v>
       </c>
       <c r="N12" t="n">
-        <v>0.419541080051806</v>
+        <v>0.4195410800518065</v>
       </c>
       <c r="O12" t="n">
         <v>5.432101010797401</v>
       </c>
       <c r="P12" t="n">
-        <v>0.04527376770269571</v>
+        <v>0.04527376770269594</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.748141873036399</v>
+        <v>0.7481418730364023</v>
       </c>
       <c r="R12" t="n">
         <v>0.6381325211448932</v>
@@ -1752,37 +1752,37 @@
         <v>0.8101334032030804</v>
       </c>
       <c r="H13" t="n">
-        <v>0.07882605812933426</v>
+        <v>0.07882605812933424</v>
       </c>
       <c r="I13" t="n">
-        <v>3.29991292409335</v>
+        <v>3.299912924093349</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4307968715834936</v>
+        <v>0.4307968715834937</v>
       </c>
       <c r="K13" t="n">
         <v>9.044486053901261</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1060025340359008</v>
+        <v>-0.1060025340359006</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.513621886177809</v>
+        <v>-1.513621886177807</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03833813474023231</v>
+        <v>0.03833813474023236</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4911438545488206</v>
+        <v>0.491143854548821</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1015017459043074</v>
+        <v>0.1015017459043075</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.343657160662783</v>
+        <v>2.343657160662784</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2136196510592738</v>
+        <v>0.2136196510592737</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1857,10 +1857,10 @@
         <v>2.412718548306209</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05639698344970885</v>
+        <v>0.05639698344970881</v>
       </c>
       <c r="I14" t="n">
-        <v>2.365989162713668</v>
+        <v>2.365989162713666</v>
       </c>
       <c r="J14" t="n">
         <v>0.6648623680493825</v>
@@ -1869,22 +1869,22 @@
         <v>11.60052164084876</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1177874448733583</v>
+        <v>0.1177874448733586</v>
       </c>
       <c r="M14" t="n">
-        <v>1.327348222436577</v>
+        <v>1.32734822243658</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3470982971272106</v>
+        <v>0.347098297127211</v>
       </c>
       <c r="O14" t="n">
-        <v>4.582375557670485</v>
+        <v>4.582375557670487</v>
       </c>
       <c r="P14" t="n">
-        <v>0.08293399441461619</v>
+        <v>0.08293399441461635</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.43433383734736</v>
+        <v>1.434333837347362</v>
       </c>
       <c r="R14" t="n">
         <v>0.4601514914854684</v>
@@ -1965,28 +1965,28 @@
         <v>0.2599832314706374</v>
       </c>
       <c r="I15" t="n">
-        <v>4.597225654906017</v>
+        <v>4.597225654906018</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3826305032740539</v>
+        <v>0.3826305032740536</v>
       </c>
       <c r="K15" t="n">
-        <v>3.183259239684164</v>
+        <v>3.183259239684162</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03620967970936637</v>
+        <v>0.03620967970936656</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1347223468975744</v>
+        <v>0.1347223468975751</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5487142810344026</v>
+        <v>0.5487142810344033</v>
       </c>
       <c r="O15" t="n">
-        <v>3.31975420076438</v>
+        <v>3.319754200764385</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2524445386728309</v>
+        <v>-0.252444538672831</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.609962991172408</v>
@@ -2067,34 +2067,34 @@
         <v>7.020975029305385</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1685586158602541</v>
+        <v>0.168558615860254</v>
       </c>
       <c r="I16" t="n">
-        <v>2.519314730496677</v>
+        <v>2.519314730496676</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8502104962281525</v>
+        <v>0.8502104962281527</v>
       </c>
       <c r="K16" t="n">
-        <v>5.449775465229427</v>
+        <v>5.449775465229429</v>
       </c>
       <c r="L16" t="n">
-        <v>0.007830305514628072</v>
+        <v>0.007830305514628488</v>
       </c>
       <c r="M16" t="n">
-        <v>0.03687169275630593</v>
+        <v>0.03687169275630788</v>
       </c>
       <c r="N16" t="n">
-        <v>0.719610158657974</v>
+        <v>0.7196101586579741</v>
       </c>
       <c r="O16" t="n">
         <v>3.428021522775981</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3493834822585233</v>
+        <v>0.3493834822585236</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.229577976569388</v>
+        <v>2.229577976569389</v>
       </c>
       <c r="R16" t="n">
         <v>0.1528159617370626</v>
@@ -2172,34 +2172,34 @@
         <v>0.90916746224333</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1032515517448015</v>
+        <v>0.1032515517448014</v>
       </c>
       <c r="I17" t="n">
         <v>4.169549904783453</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8003599385743806</v>
+        <v>0.8003599385743805</v>
       </c>
       <c r="K17" t="n">
         <v>15.02761421798034</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2384651847936584</v>
+        <v>0.2384651847936587</v>
       </c>
       <c r="M17" t="n">
-        <v>3.06245216811059</v>
+        <v>3.062452168110595</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5274877701549222</v>
+        <v>0.527487770154923</v>
       </c>
       <c r="O17" t="n">
-        <v>6.412758050078818</v>
+        <v>6.412758050078825</v>
       </c>
       <c r="P17" t="n">
         <v>-0.1882134918440016</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.985580478048793</v>
+        <v>-2.985580478048792</v>
       </c>
       <c r="R17" t="n">
         <v>0.6430352687834047</v>
@@ -2280,34 +2280,34 @@
         <v>0.1169573586926704</v>
       </c>
       <c r="I18" t="n">
-        <v>4.746649516992666</v>
+        <v>4.746649516992664</v>
       </c>
       <c r="J18" t="n">
         <v>0.7859232309686279</v>
       </c>
       <c r="K18" t="n">
-        <v>15.29677294898078</v>
+        <v>15.29677294898077</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2091737112758189</v>
+        <v>0.2091737112758191</v>
       </c>
       <c r="M18" t="n">
-        <v>2.700514691978571</v>
+        <v>2.700514691978574</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4754339074993205</v>
+        <v>0.4754339074993211</v>
       </c>
       <c r="O18" t="n">
-        <v>5.926012549533326</v>
+        <v>5.926012549533331</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1634977148894132</v>
+        <v>-0.1634977148894131</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.689362752009022</v>
+        <v>-2.689362752009017</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6209528162453047</v>
+        <v>0.6209528162453049</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2382,37 +2382,37 @@
         <v>0.8101334032030804</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07882605812933426</v>
+        <v>0.07882605812933424</v>
       </c>
       <c r="I19" t="n">
-        <v>3.29991292409335</v>
+        <v>3.299912924093349</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4307968715834936</v>
+        <v>0.4307968715834937</v>
       </c>
       <c r="K19" t="n">
         <v>9.044486053901261</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1060025340359008</v>
+        <v>-0.1060025340359006</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.513621886177809</v>
+        <v>-1.513621886177807</v>
       </c>
       <c r="N19" t="n">
-        <v>0.03833813474023231</v>
+        <v>0.03833813474023236</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4911438545488206</v>
+        <v>0.491143854548821</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1015017459043074</v>
+        <v>0.1015017459043075</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.343657160662783</v>
+        <v>2.343657160662784</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2136196510592738</v>
+        <v>0.2136196510592737</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2490,31 +2490,31 @@
         <v>0.118026185165393</v>
       </c>
       <c r="I20" t="n">
-        <v>4.941358889152037</v>
+        <v>4.941358889152035</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4514042675795885</v>
+        <v>0.4514042675795884</v>
       </c>
       <c r="K20" t="n">
-        <v>9.41840748584775</v>
+        <v>9.418407485847748</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06846194813366152</v>
+        <v>0.06846194813366166</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9827008227095834</v>
+        <v>0.9827008227095858</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3665411162099903</v>
+        <v>0.3665411162099906</v>
       </c>
       <c r="O20" t="n">
-        <v>4.827747058998603</v>
+        <v>4.827747058998606</v>
       </c>
       <c r="P20" t="n">
         <v>-0.1189633043708004</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.057906158827559</v>
+        <v>-2.057906158827558</v>
       </c>
       <c r="R20" t="n">
         <v>0.3846644102401878</v>
@@ -2595,28 +2595,28 @@
         <v>0.2599832314706374</v>
       </c>
       <c r="I21" t="n">
-        <v>4.597225654906017</v>
+        <v>4.597225654906018</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3826305032740539</v>
+        <v>0.3826305032740536</v>
       </c>
       <c r="K21" t="n">
-        <v>3.183259239684164</v>
+        <v>3.183259239684162</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03620967970936637</v>
+        <v>0.03620967970936656</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1347223468975744</v>
+        <v>0.1347223468975751</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5487142810344026</v>
+        <v>0.5487142810344033</v>
       </c>
       <c r="O21" t="n">
-        <v>3.31975420076438</v>
+        <v>3.319754200764385</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2524445386728309</v>
+        <v>-0.252444538672831</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.609962991172408</v>
@@ -2697,31 +2697,31 @@
         <v>2.788246106422154</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3430319789277412</v>
+        <v>0.3430319789277413</v>
       </c>
       <c r="I22" t="n">
         <v>5.357176871475987</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2523820043373254</v>
+        <v>0.2523820043373252</v>
       </c>
       <c r="K22" t="n">
-        <v>2.002319985200463</v>
+        <v>2.00231998520046</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2274331188817208</v>
+        <v>-0.2274331188817206</v>
       </c>
       <c r="M22" t="n">
         <v>-1.30345049497981</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6130410031260654</v>
+        <v>0.6130410031260659</v>
       </c>
       <c r="O22" t="n">
-        <v>3.145480864401485</v>
+        <v>3.145480864401486</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2040526458643821</v>
+        <v>-0.2040526458643822</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.345371442690972</v>
